--- a/data/projects/56A0TXN/早期介入/交付预案/解析结果/预案草稿/3.部件配置信息.xlsx
+++ b/data/projects/56A0TXN/早期介入/交付预案/解析结果/预案草稿/3.部件配置信息.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,20 +451,74 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BF3</t>
+          <t>BF3-DPU-400</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>伙伴</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>BlueField</t>
+          <t>BlueField-3 DPU 智能网卡</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ascend-910C</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>昇腾 910C 训练处理器</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>网卡</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CX7-400G</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>伙伴</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ConnectX-7 400G NIC</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>人工录入</t>
         </is>
